--- a/marketing_report/outputs/Grado_Pregrado/tabla_utm_campaigns.xlsx
+++ b/marketing_report/outputs/Grado_Pregrado/tabla_utm_campaigns.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="131">
   <si>
     <t>UtmCampaign</t>
   </si>
@@ -82,15 +82,15 @@
     <t>19230946036</t>
   </si>
   <si>
+    <t>15360035696</t>
+  </si>
+  <si>
+    <t>14892996169</t>
+  </si>
+  <si>
     <t>21772187688</t>
   </si>
   <si>
-    <t>15360035696</t>
-  </si>
-  <si>
-    <t>14892996169</t>
-  </si>
-  <si>
     <t>14899816755</t>
   </si>
   <si>
@@ -109,12 +109,12 @@
     <t>14905247697</t>
   </si>
   <si>
+    <t>14891543883</t>
+  </si>
+  <si>
     <t>23497387174</t>
   </si>
   <si>
-    <t>14891543883</t>
-  </si>
-  <si>
     <t>14906054625</t>
   </si>
   <si>
@@ -130,19 +130,22 @@
     <t>14909096324</t>
   </si>
   <si>
+    <t>14894392756</t>
+  </si>
+  <si>
     <t>14894109331</t>
   </si>
   <si>
-    <t>14894392756</t>
-  </si>
-  <si>
     <t>15232856055</t>
   </si>
   <si>
+    <t>16552752228</t>
+  </si>
+  <si>
     <t>22644502976</t>
   </si>
   <si>
-    <t>16552752228</t>
+    <t>23277494379</t>
   </si>
   <si>
     <t>14905339848</t>
@@ -160,30 +163,27 @@
     <t>8357919511</t>
   </si>
   <si>
+    <t>[otra_campania]</t>
+  </si>
+  <si>
     <t>23044564068</t>
   </si>
   <si>
     <t>14905619205</t>
   </si>
   <si>
-    <t>23277494379</t>
-  </si>
-  <si>
-    <t>[otra_campania]</t>
-  </si>
-  <si>
     <t>16515402374</t>
   </si>
   <si>
+    <t>120235998797960048</t>
+  </si>
+  <si>
+    <t>TCAR_TMOD_PREYGRA_MAIL_LEAD_1INGRESO26_1_PRESENTACION</t>
+  </si>
+  <si>
     <t>Paso 1 - Journey PyG</t>
   </si>
   <si>
-    <t>120235998797960048</t>
-  </si>
-  <si>
-    <t>TCAR_TMOD_PREYGRA_MAIL_LEAD_1INGRESO26_1_PRESENTACION</t>
-  </si>
-  <si>
     <t>validacion</t>
   </si>
   <si>
@@ -205,88 +205,100 @@
     <t>22647879775</t>
   </si>
   <si>
+    <t>120236406788520048</t>
+  </si>
+  <si>
+    <t>6613618927007</t>
+  </si>
+  <si>
     <t>20998371077</t>
   </si>
   <si>
-    <t>120236406788520048</t>
-  </si>
-  <si>
     <t>22758675353</t>
   </si>
   <si>
-    <t>6613618927007</t>
+    <t>20531309410</t>
   </si>
   <si>
     <t>Paso2- Prueba Angie y Edu -Presencial</t>
   </si>
   <si>
-    <t>20531309410</t>
-  </si>
-  <si>
     <t>15034800468</t>
   </si>
   <si>
+    <t>15773753483</t>
+  </si>
+  <si>
     <t>TCAR_TMOD_PREYGRA_MAIL_LEAD_1INGRESO26_3_SI_TRESPASOS</t>
   </si>
   <si>
     <t>120211991684880189</t>
   </si>
   <si>
+    <t>TCAR_TMOD_PREYGRA_MAIL_LEAD_1INGRESO26_4_SI_CIERRE</t>
+  </si>
+  <si>
+    <t>TCAR_TMOD_PREYGRA_MAIL_LEAD_1INGRESO26_2_PRESENCIAL</t>
+  </si>
+  <si>
+    <t>TCAR_TMOD_PREYGRA_MAIL_LEAD_1INGRESO26_3_NO_TESTIMONIAL</t>
+  </si>
+  <si>
     <t>ingreso2016</t>
   </si>
   <si>
-    <t>TCAR_TMOD_PREYGRA_MAIL_LEAD_1INGRESO26_2_PRESENCIAL</t>
+    <t>FCI Modo Home</t>
+  </si>
+  <si>
+    <t>20523462698</t>
   </si>
   <si>
     <t>sms-2025-05-08-2dacohorte</t>
   </si>
   <si>
-    <t>FCI Modo Home</t>
-  </si>
-  <si>
-    <t>TCAR_TMOD_PREYGRA_MAIL_LEAD_1INGRESO26_3_NO_TESTIMONIAL</t>
-  </si>
-  <si>
     <t>Paso 3 - Journey PyG</t>
   </si>
   <si>
-    <t>20523462698</t>
+    <t>Paso 5 - Journey PyG</t>
+  </si>
+  <si>
+    <t>14941637467</t>
+  </si>
+  <si>
+    <t>15034827564</t>
+  </si>
+  <si>
+    <t>21778508075</t>
+  </si>
+  <si>
+    <t>TCAR_VIRTUAL_PREYGRA_MAIL_LEAD_1INGRESO26_4_NO_CIERRE</t>
+  </si>
+  <si>
+    <t>23041074431</t>
+  </si>
+  <si>
+    <t>22637500317</t>
   </si>
   <si>
     <t>120217617380780655</t>
   </si>
   <si>
-    <t>21778508075</t>
-  </si>
-  <si>
-    <t>23041074431</t>
-  </si>
-  <si>
-    <t>22637500317</t>
-  </si>
-  <si>
-    <t>TCAR_TMOD_PREYGRA_MAIL_LEAD_1INGRESO26_4_SI_CIERRE</t>
-  </si>
-  <si>
-    <t>Paso 5 - Journey PyG</t>
-  </si>
-  <si>
     <t>posgrados</t>
   </si>
   <si>
     <t>120218321739580030</t>
   </si>
   <si>
+    <t>21933203642</t>
+  </si>
+  <si>
+    <t>TCAR_PRESENCIAL_PREYGRA_MAIL_LEAD_1INGRESO26_4_NO_CIERRE</t>
+  </si>
+  <si>
     <t>21996147342</t>
   </si>
   <si>
-    <t>21933203642</t>
-  </si>
-  <si>
-    <t>TCAR_VIRTUAL_PREYGRA_MAIL_LEAD_1INGRESO26_4_NO_CIERRE</t>
-  </si>
-  <si>
-    <t>TCAR_PRESENCIAL_PREYGRA_MAIL_LEAD_1INGRESO26_4_NO_CIERRE</t>
+    <t>web</t>
   </si>
   <si>
     <t>branding</t>
@@ -298,48 +310,42 @@
     <t>Paso5- Prueba Angie y Edu -Presencial</t>
   </si>
   <si>
+    <t>20917818431</t>
+  </si>
+  <si>
+    <t>12018552619</t>
+  </si>
+  <si>
+    <t>120217591475740655</t>
+  </si>
+  <si>
+    <t>120218149356610655</t>
+  </si>
+  <si>
+    <t>120218590009620655</t>
+  </si>
+  <si>
+    <t>120238934940150048</t>
+  </si>
+  <si>
     <t>15069068625</t>
   </si>
   <si>
-    <t>12018552619</t>
-  </si>
-  <si>
-    <t>120217591475740655</t>
-  </si>
-  <si>
-    <t>120218149356610655</t>
-  </si>
-  <si>
-    <t>120218590009620655</t>
-  </si>
-  <si>
-    <t>120238934940150048</t>
-  </si>
-  <si>
-    <t>14941637467</t>
-  </si>
-  <si>
-    <t>15034827564</t>
-  </si>
-  <si>
-    <t>15773753483</t>
+    <t>20998490630</t>
   </si>
   <si>
     <t>Paso 4 - Journey PyG  - V2</t>
   </si>
   <si>
-    <t>20917818431</t>
-  </si>
-  <si>
-    <t>20998490630</t>
-  </si>
-  <si>
     <t>22454462079</t>
   </si>
   <si>
     <t>23040805580</t>
   </si>
   <si>
+    <t>23220287690</t>
+  </si>
+  <si>
     <t>23255356694</t>
   </si>
   <si>
@@ -349,7 +355,7 @@
     <t>6793315519607</t>
   </si>
   <si>
-    <t>web</t>
+    <t>15073321634</t>
   </si>
   <si>
     <t>facebook</t>
@@ -758,7 +764,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H105"/>
+  <dimension ref="A1:H107"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -792,25 +798,25 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D2">
-        <v>12683</v>
+        <v>13235</v>
       </c>
       <c r="E2">
-        <v>11308</v>
+        <v>11766</v>
       </c>
       <c r="F2">
-        <v>3216</v>
+        <v>5148</v>
       </c>
       <c r="G2">
-        <v>54</v>
+        <v>96</v>
       </c>
       <c r="H2">
-        <v>1.68</v>
+        <v>1.86</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -818,25 +824,25 @@
         <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C3" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D3">
-        <v>7353</v>
+        <v>8244</v>
       </c>
       <c r="E3">
-        <v>5812</v>
+        <v>6529</v>
       </c>
       <c r="F3">
-        <v>539</v>
+        <v>6679</v>
       </c>
       <c r="G3">
-        <v>52</v>
+        <v>748</v>
       </c>
       <c r="H3">
-        <v>9.65</v>
+        <v>11.2</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -844,25 +850,25 @@
         <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C4" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="D4">
-        <v>5603</v>
+        <v>6089</v>
       </c>
       <c r="E4">
-        <v>5243</v>
+        <v>5662</v>
       </c>
       <c r="F4">
-        <v>1282</v>
+        <v>2765</v>
       </c>
       <c r="G4">
-        <v>8</v>
+        <v>58</v>
       </c>
       <c r="H4">
-        <v>0.62</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -870,25 +876,25 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C5" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D5">
-        <v>5415</v>
+        <v>5560</v>
       </c>
       <c r="E5">
-        <v>4819</v>
+        <v>4940</v>
       </c>
       <c r="F5">
-        <v>1326</v>
+        <v>1180</v>
       </c>
       <c r="G5">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H5">
-        <v>2.11</v>
+        <v>2.54</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -896,25 +902,25 @@
         <v>12</v>
       </c>
       <c r="B6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C6" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D6">
-        <v>5308</v>
+        <v>5324</v>
       </c>
       <c r="E6">
-        <v>4229</v>
+        <v>4228</v>
       </c>
       <c r="F6">
-        <v>501</v>
+        <v>0</v>
       </c>
       <c r="G6">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="H6">
-        <v>3.99</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -922,25 +928,25 @@
         <v>13</v>
       </c>
       <c r="B7" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C7" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="D7">
-        <v>4234</v>
+        <v>4645</v>
       </c>
       <c r="E7">
-        <v>3631</v>
+        <v>3992</v>
       </c>
       <c r="F7">
-        <v>678</v>
+        <v>4029</v>
       </c>
       <c r="G7">
-        <v>27</v>
+        <v>176</v>
       </c>
       <c r="H7">
-        <v>3.98</v>
+        <v>4.37</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -948,25 +954,25 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C8" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D8">
-        <v>2966</v>
+        <v>3477</v>
       </c>
       <c r="E8">
-        <v>2604</v>
+        <v>3057</v>
       </c>
       <c r="F8">
-        <v>723</v>
+        <v>3078</v>
       </c>
       <c r="G8">
-        <v>52</v>
+        <v>207</v>
       </c>
       <c r="H8">
-        <v>7.19</v>
+        <v>6.73</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -974,25 +980,25 @@
         <v>15</v>
       </c>
       <c r="B9" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C9" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D9">
-        <v>1678</v>
+        <v>1736</v>
       </c>
       <c r="E9">
-        <v>1497</v>
+        <v>1544</v>
       </c>
       <c r="F9">
-        <v>385</v>
+        <v>535</v>
       </c>
       <c r="G9">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="H9">
-        <v>5.45</v>
+        <v>5.23</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -1000,25 +1006,25 @@
         <v>16</v>
       </c>
       <c r="B10" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C10" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D10">
-        <v>1563</v>
+        <v>1593</v>
       </c>
       <c r="E10">
-        <v>1446</v>
+        <v>1473</v>
       </c>
       <c r="F10">
-        <v>337</v>
+        <v>592</v>
       </c>
       <c r="G10">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="H10">
-        <v>1.78</v>
+        <v>3.38</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -1026,25 +1032,25 @@
         <v>17</v>
       </c>
       <c r="B11" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C11" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D11">
-        <v>1141</v>
+        <v>1190</v>
       </c>
       <c r="E11">
-        <v>1011</v>
+        <v>1048</v>
       </c>
       <c r="F11">
-        <v>312</v>
+        <v>357</v>
       </c>
       <c r="G11">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="H11">
-        <v>1.6</v>
+        <v>4.76</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -1052,25 +1058,25 @@
         <v>18</v>
       </c>
       <c r="B12" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C12" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D12">
-        <v>1090</v>
+        <v>1135</v>
       </c>
       <c r="E12">
-        <v>969</v>
+        <v>1003</v>
       </c>
       <c r="F12">
-        <v>263</v>
+        <v>465</v>
       </c>
       <c r="G12">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H12">
-        <v>0.38</v>
+        <v>1.08</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -1078,25 +1084,25 @@
         <v>19</v>
       </c>
       <c r="B13" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C13" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D13">
-        <v>1018</v>
+        <v>1067</v>
       </c>
       <c r="E13">
-        <v>908</v>
+        <v>952</v>
       </c>
       <c r="F13">
-        <v>198</v>
+        <v>475</v>
       </c>
       <c r="G13">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="H13">
-        <v>1.01</v>
+        <v>1.47</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -1104,25 +1110,25 @@
         <v>20</v>
       </c>
       <c r="B14" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C14" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D14">
-        <v>995</v>
+        <v>1010</v>
       </c>
       <c r="E14">
-        <v>897</v>
+        <v>908</v>
       </c>
       <c r="F14">
-        <v>229</v>
+        <v>343</v>
       </c>
       <c r="G14">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="H14">
-        <v>3.93</v>
+        <v>3.79</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -1130,25 +1136,25 @@
         <v>21</v>
       </c>
       <c r="B15" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C15" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D15">
-        <v>898</v>
+        <v>926</v>
       </c>
       <c r="E15">
-        <v>817</v>
+        <v>838</v>
       </c>
       <c r="F15">
-        <v>184</v>
+        <v>303</v>
       </c>
       <c r="G15">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="H15">
-        <v>4.35</v>
+        <v>3.63</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -1156,25 +1162,25 @@
         <v>22</v>
       </c>
       <c r="B16" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C16" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D16">
-        <v>754</v>
+        <v>845</v>
       </c>
       <c r="E16">
-        <v>705</v>
+        <v>723</v>
       </c>
       <c r="F16">
-        <v>84</v>
+        <v>435</v>
       </c>
       <c r="G16">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="H16">
-        <v>0</v>
+        <v>2.53</v>
       </c>
     </row>
     <row r="17" spans="1:8">
@@ -1182,25 +1188,25 @@
         <v>23</v>
       </c>
       <c r="B17" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C17" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D17">
-        <v>815</v>
+        <v>793</v>
       </c>
       <c r="E17">
-        <v>700</v>
+        <v>718</v>
       </c>
       <c r="F17">
-        <v>122</v>
+        <v>302</v>
       </c>
       <c r="G17">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="H17">
-        <v>1.64</v>
+        <v>3.97</v>
       </c>
     </row>
     <row r="18" spans="1:8">
@@ -1208,25 +1214,25 @@
         <v>24</v>
       </c>
       <c r="B18" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C18" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D18">
-        <v>767</v>
+        <v>755</v>
       </c>
       <c r="E18">
-        <v>696</v>
+        <v>705</v>
       </c>
       <c r="F18">
-        <v>178</v>
+        <v>0</v>
       </c>
       <c r="G18">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H18">
-        <v>2.81</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:8">
@@ -1234,25 +1240,25 @@
         <v>25</v>
       </c>
       <c r="B19" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C19" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D19">
-        <v>699</v>
+        <v>716</v>
       </c>
       <c r="E19">
-        <v>627</v>
+        <v>640</v>
       </c>
       <c r="F19">
-        <v>178</v>
+        <v>213</v>
       </c>
       <c r="G19">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="H19">
-        <v>0.5600000000000001</v>
+        <v>3.76</v>
       </c>
     </row>
     <row r="20" spans="1:8">
@@ -1260,25 +1266,25 @@
         <v>26</v>
       </c>
       <c r="B20" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C20" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D20">
-        <v>653</v>
+        <v>692</v>
       </c>
       <c r="E20">
-        <v>584</v>
+        <v>620</v>
       </c>
       <c r="F20">
-        <v>139</v>
+        <v>295</v>
       </c>
       <c r="G20">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="H20">
-        <v>2.16</v>
+        <v>4.07</v>
       </c>
     </row>
     <row r="21" spans="1:8">
@@ -1286,25 +1292,25 @@
         <v>27</v>
       </c>
       <c r="B21" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C21" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D21">
-        <v>646</v>
+        <v>684</v>
       </c>
       <c r="E21">
-        <v>578</v>
+        <v>608</v>
       </c>
       <c r="F21">
-        <v>134</v>
+        <v>254</v>
       </c>
       <c r="G21">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="H21">
-        <v>2.99</v>
+        <v>3.54</v>
       </c>
     </row>
     <row r="22" spans="1:8">
@@ -1312,25 +1318,25 @@
         <v>28</v>
       </c>
       <c r="B22" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C22" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D22">
-        <v>628</v>
+        <v>657</v>
       </c>
       <c r="E22">
-        <v>552</v>
+        <v>576</v>
       </c>
       <c r="F22">
-        <v>124</v>
+        <v>277</v>
       </c>
       <c r="G22">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="H22">
-        <v>3.23</v>
+        <v>4.69</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -1338,25 +1344,25 @@
         <v>29</v>
       </c>
       <c r="B23" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C23" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D23">
-        <v>593</v>
+        <v>617</v>
       </c>
       <c r="E23">
-        <v>527</v>
+        <v>546</v>
       </c>
       <c r="F23">
-        <v>115</v>
+        <v>232</v>
       </c>
       <c r="G23">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="H23">
-        <v>3.48</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="24" spans="1:8">
@@ -1364,25 +1370,25 @@
         <v>30</v>
       </c>
       <c r="B24" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C24" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D24">
-        <v>566</v>
+        <v>603</v>
       </c>
       <c r="E24">
-        <v>514</v>
+        <v>541</v>
       </c>
       <c r="F24">
-        <v>120</v>
+        <v>319</v>
       </c>
       <c r="G24">
         <v>2</v>
       </c>
       <c r="H24">
-        <v>1.67</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -1390,25 +1396,25 @@
         <v>31</v>
       </c>
       <c r="B25" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C25" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D25">
-        <v>550</v>
+        <v>563</v>
       </c>
       <c r="E25">
-        <v>486</v>
+        <v>497</v>
       </c>
       <c r="F25">
-        <v>278</v>
+        <v>192</v>
       </c>
       <c r="G25">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H25">
-        <v>3.6</v>
+        <v>3.12</v>
       </c>
     </row>
     <row r="26" spans="1:8">
@@ -1416,25 +1422,25 @@
         <v>32</v>
       </c>
       <c r="B26" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C26" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D26">
-        <v>544</v>
+        <v>550</v>
       </c>
       <c r="E26">
-        <v>481</v>
+        <v>486</v>
       </c>
       <c r="F26">
-        <v>80</v>
+        <v>486</v>
       </c>
       <c r="G26">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="H26">
-        <v>0</v>
+        <v>3.91</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -1442,25 +1448,25 @@
         <v>33</v>
       </c>
       <c r="B27" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C27" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D27">
-        <v>494</v>
+        <v>520</v>
       </c>
       <c r="E27">
-        <v>443</v>
+        <v>467</v>
       </c>
       <c r="F27">
-        <v>112</v>
+        <v>210</v>
       </c>
       <c r="G27">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H27">
-        <v>2.68</v>
+        <v>2.86</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -1468,25 +1474,25 @@
         <v>34</v>
       </c>
       <c r="B28" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C28" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D28">
-        <v>479</v>
+        <v>513</v>
       </c>
       <c r="E28">
-        <v>407</v>
+        <v>436</v>
       </c>
       <c r="F28">
-        <v>112</v>
+        <v>163</v>
       </c>
       <c r="G28">
         <v>1</v>
       </c>
       <c r="H28">
-        <v>0.89</v>
+        <v>0.61</v>
       </c>
     </row>
     <row r="29" spans="1:8">
@@ -1494,25 +1500,25 @@
         <v>35</v>
       </c>
       <c r="B29" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C29" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D29">
-        <v>453</v>
+        <v>478</v>
       </c>
       <c r="E29">
-        <v>402</v>
+        <v>424</v>
       </c>
       <c r="F29">
-        <v>104</v>
+        <v>162</v>
       </c>
       <c r="G29">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H29">
-        <v>0</v>
+        <v>1.85</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -1520,25 +1526,25 @@
         <v>36</v>
       </c>
       <c r="B30" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C30" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D30">
-        <v>384</v>
+        <v>394</v>
       </c>
       <c r="E30">
-        <v>355</v>
+        <v>362</v>
       </c>
       <c r="F30">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="G30">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="H30">
-        <v>3.49</v>
+        <v>7.69</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -1546,25 +1552,25 @@
         <v>37</v>
       </c>
       <c r="B31" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C31" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D31">
-        <v>336</v>
+        <v>352</v>
       </c>
       <c r="E31">
-        <v>298</v>
+        <v>311</v>
       </c>
       <c r="F31">
-        <v>67</v>
+        <v>130</v>
       </c>
       <c r="G31">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="H31">
-        <v>5.97</v>
+        <v>10.77</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -1572,25 +1578,25 @@
         <v>38</v>
       </c>
       <c r="B32" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C32" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D32">
-        <v>325</v>
+        <v>348</v>
       </c>
       <c r="E32">
-        <v>285</v>
+        <v>302</v>
       </c>
       <c r="F32">
-        <v>67</v>
+        <v>137</v>
       </c>
       <c r="G32">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="H32">
-        <v>8.960000000000001</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="33" spans="1:8">
@@ -1598,25 +1604,25 @@
         <v>39</v>
       </c>
       <c r="B33" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C33" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D33">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="E33">
-        <v>281</v>
+        <v>289</v>
       </c>
       <c r="F33">
-        <v>72</v>
+        <v>87</v>
       </c>
       <c r="G33">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="H33">
-        <v>4.17</v>
+        <v>10.34</v>
       </c>
     </row>
     <row r="34" spans="1:8">
@@ -1624,25 +1630,25 @@
         <v>40</v>
       </c>
       <c r="B34" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C34" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D34">
-        <v>285</v>
+        <v>305</v>
       </c>
       <c r="E34">
-        <v>242</v>
+        <v>260</v>
       </c>
       <c r="F34">
-        <v>50</v>
+        <v>127</v>
       </c>
       <c r="G34">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="H34">
-        <v>16</v>
+        <v>11.81</v>
       </c>
     </row>
     <row r="35" spans="1:8">
@@ -1650,25 +1656,25 @@
         <v>41</v>
       </c>
       <c r="B35" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C35" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D35">
-        <v>234</v>
+        <v>258</v>
       </c>
       <c r="E35">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="F35">
-        <v>42</v>
+        <v>167</v>
       </c>
       <c r="G35">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H35">
-        <v>0</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="36" spans="1:8">
@@ -1676,25 +1682,25 @@
         <v>42</v>
       </c>
       <c r="B36" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C36" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="D36">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E36">
-        <v>210</v>
+        <v>224</v>
       </c>
       <c r="F36">
-        <v>35</v>
+        <v>152</v>
       </c>
       <c r="G36">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H36">
-        <v>2.86</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:8">
@@ -1702,25 +1708,22 @@
         <v>43</v>
       </c>
       <c r="B37" t="s">
-        <v>46</v>
-      </c>
-      <c r="C37" t="s">
-        <v>119</v>
+        <v>47</v>
       </c>
       <c r="D37">
-        <v>179</v>
+        <v>210</v>
       </c>
       <c r="E37">
-        <v>166</v>
+        <v>177</v>
       </c>
       <c r="F37">
-        <v>38</v>
+        <v>183</v>
       </c>
       <c r="G37">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="H37">
-        <v>0</v>
+        <v>6.56</v>
       </c>
     </row>
     <row r="38" spans="1:8">
@@ -1728,19 +1731,19 @@
         <v>44</v>
       </c>
       <c r="B38" t="s">
-        <v>111</v>
+        <v>47</v>
       </c>
       <c r="C38" t="s">
-        <v>13</v>
+        <v>121</v>
       </c>
       <c r="D38">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="E38">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="F38">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="G38">
         <v>0</v>
@@ -1754,19 +1757,19 @@
         <v>45</v>
       </c>
       <c r="B39" t="s">
-        <v>46</v>
+        <v>94</v>
       </c>
       <c r="C39" t="s">
-        <v>119</v>
+        <v>13</v>
       </c>
       <c r="D39">
-        <v>150</v>
+        <v>183</v>
       </c>
       <c r="E39">
-        <v>142</v>
+        <v>167</v>
       </c>
       <c r="F39">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="G39">
         <v>0</v>
@@ -1780,25 +1783,25 @@
         <v>46</v>
       </c>
       <c r="B40" t="s">
-        <v>114</v>
+        <v>47</v>
       </c>
       <c r="C40" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D40">
-        <v>125</v>
+        <v>171</v>
       </c>
       <c r="E40">
-        <v>117</v>
+        <v>162</v>
       </c>
       <c r="F40">
-        <v>53</v>
+        <v>162</v>
       </c>
       <c r="G40">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H40">
-        <v>0</v>
+        <v>2.47</v>
       </c>
     </row>
     <row r="41" spans="1:8">
@@ -1806,19 +1809,19 @@
         <v>47</v>
       </c>
       <c r="B41" t="s">
-        <v>46</v>
+        <v>116</v>
       </c>
       <c r="C41" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D41">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="E41">
-        <v>101</v>
+        <v>117</v>
       </c>
       <c r="F41">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="G41">
         <v>0</v>
@@ -1832,19 +1835,19 @@
         <v>48</v>
       </c>
       <c r="B42" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C42" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D42">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E42">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="F42">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G42">
         <v>0</v>
@@ -1858,25 +1861,25 @@
         <v>49</v>
       </c>
       <c r="B43" t="s">
-        <v>46</v>
+        <v>117</v>
       </c>
       <c r="C43" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="D43">
-        <v>92</v>
+        <v>132</v>
       </c>
       <c r="E43">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="F43">
-        <v>16</v>
+        <v>63</v>
       </c>
       <c r="G43">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H43">
-        <v>6.25</v>
+        <v>9.52</v>
       </c>
     </row>
     <row r="44" spans="1:8">
@@ -1884,22 +1887,25 @@
         <v>50</v>
       </c>
       <c r="B44" t="s">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="C44" t="s">
+        <v>121</v>
       </c>
       <c r="D44">
-        <v>87</v>
+        <v>113</v>
       </c>
       <c r="E44">
-        <v>72</v>
+        <v>97</v>
       </c>
       <c r="F44">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="G44">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="H44">
-        <v>0</v>
+        <v>11.11</v>
       </c>
     </row>
     <row r="45" spans="1:8">
@@ -1907,25 +1913,25 @@
         <v>51</v>
       </c>
       <c r="B45" t="s">
-        <v>115</v>
+        <v>47</v>
       </c>
       <c r="C45" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="D45">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="E45">
-        <v>59</v>
+        <v>91</v>
       </c>
       <c r="F45">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="G45">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H45">
-        <v>0</v>
+        <v>9.380000000000001</v>
       </c>
     </row>
     <row r="46" spans="1:8">
@@ -1933,25 +1939,25 @@
         <v>52</v>
       </c>
       <c r="B46" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C46" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D46">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="E46">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F46">
-        <v>9</v>
+        <v>47</v>
       </c>
       <c r="G46">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H46">
-        <v>0</v>
+        <v>8.51</v>
       </c>
     </row>
     <row r="47" spans="1:8">
@@ -1959,25 +1965,25 @@
         <v>53</v>
       </c>
       <c r="B47" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="C47" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="D47">
-        <v>43</v>
+        <v>62</v>
       </c>
       <c r="E47">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="F47">
-        <v>17</v>
+        <v>51</v>
       </c>
       <c r="G47">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H47">
-        <v>0</v>
+        <v>1.96</v>
       </c>
     </row>
     <row r="48" spans="1:8">
@@ -1985,25 +1991,25 @@
         <v>54</v>
       </c>
       <c r="B48" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C48" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D48">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="E48">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="F48">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="G48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H48">
-        <v>0</v>
+        <v>2.27</v>
       </c>
     </row>
     <row r="49" spans="1:8">
@@ -2011,19 +2017,19 @@
         <v>55</v>
       </c>
       <c r="B49" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C49" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D49">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="E49">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="F49">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G49">
         <v>0</v>
@@ -2037,19 +2043,19 @@
         <v>56</v>
       </c>
       <c r="B50" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C50" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D50">
+        <v>33</v>
+      </c>
+      <c r="E50">
         <v>32</v>
       </c>
-      <c r="E50">
-        <v>31</v>
-      </c>
       <c r="F50">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="G50">
         <v>0</v>
@@ -2063,10 +2069,10 @@
         <v>57</v>
       </c>
       <c r="B51" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C51" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D51">
         <v>27</v>
@@ -2075,7 +2081,7 @@
         <v>24</v>
       </c>
       <c r="F51">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G51">
         <v>0</v>
@@ -2089,25 +2095,25 @@
         <v>58</v>
       </c>
       <c r="B52" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C52" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D52">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E52">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F52">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="G52">
         <v>1</v>
       </c>
       <c r="H52">
-        <v>100</v>
+        <v>4.35</v>
       </c>
     </row>
     <row r="53" spans="1:8">
@@ -2115,10 +2121,10 @@
         <v>59</v>
       </c>
       <c r="B53" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C53" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D53">
         <v>18</v>
@@ -2127,7 +2133,7 @@
         <v>17</v>
       </c>
       <c r="F53">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G53">
         <v>0</v>
@@ -2141,10 +2147,10 @@
         <v>60</v>
       </c>
       <c r="B54" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C54" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D54">
         <v>28</v>
@@ -2153,7 +2159,7 @@
         <v>17</v>
       </c>
       <c r="F54">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G54">
         <v>0</v>
@@ -2167,25 +2173,25 @@
         <v>61</v>
       </c>
       <c r="B55" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C55" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D55">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E55">
         <v>14</v>
       </c>
       <c r="F55">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="G55">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H55">
-        <v>0</v>
+        <v>7.14</v>
       </c>
     </row>
     <row r="56" spans="1:8">
@@ -2193,10 +2199,10 @@
         <v>62</v>
       </c>
       <c r="B56" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C56" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D56">
         <v>13</v>
@@ -2205,7 +2211,7 @@
         <v>12</v>
       </c>
       <c r="F56">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="G56">
         <v>0</v>
@@ -2219,25 +2225,25 @@
         <v>63</v>
       </c>
       <c r="B57" t="s">
-        <v>46</v>
+        <v>118</v>
       </c>
       <c r="C57" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="D57">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E57">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F57">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="G57">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H57">
-        <v>33.33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58" spans="1:8">
@@ -2245,13 +2251,13 @@
         <v>64</v>
       </c>
       <c r="B58" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="C58" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D58">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E58">
         <v>9</v>
@@ -2271,10 +2277,10 @@
         <v>65</v>
       </c>
       <c r="B59" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C59" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D59">
         <v>10</v>
@@ -2283,7 +2289,7 @@
         <v>9</v>
       </c>
       <c r="F59">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G59">
         <v>0</v>
@@ -2297,13 +2303,13 @@
         <v>66</v>
       </c>
       <c r="B60" t="s">
-        <v>117</v>
+        <v>47</v>
       </c>
       <c r="C60" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="D60">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E60">
         <v>9</v>
@@ -2323,19 +2329,16 @@
         <v>67</v>
       </c>
       <c r="B61" t="s">
-        <v>115</v>
-      </c>
-      <c r="C61" t="s">
-        <v>123</v>
+        <v>47</v>
       </c>
       <c r="D61">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E61">
         <v>8</v>
       </c>
       <c r="F61">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G61">
         <v>0</v>
@@ -2349,16 +2352,19 @@
         <v>68</v>
       </c>
       <c r="B62" t="s">
-        <v>46</v>
+        <v>117</v>
+      </c>
+      <c r="C62" t="s">
+        <v>125</v>
       </c>
       <c r="D62">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E62">
         <v>8</v>
       </c>
       <c r="F62">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G62">
         <v>0</v>
@@ -2372,25 +2378,25 @@
         <v>69</v>
       </c>
       <c r="B63" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C63" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D63">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E63">
         <v>7</v>
       </c>
       <c r="F63">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G63">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H63">
-        <v>0</v>
+        <v>14.29</v>
       </c>
     </row>
     <row r="64" spans="1:8">
@@ -2398,19 +2404,19 @@
         <v>70</v>
       </c>
       <c r="B64" t="s">
-        <v>115</v>
+        <v>47</v>
       </c>
       <c r="C64" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="D64">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E64">
         <v>7</v>
       </c>
       <c r="F64">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G64">
         <v>0</v>
@@ -2427,22 +2433,22 @@
         <v>117</v>
       </c>
       <c r="C65" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D65">
         <v>7</v>
       </c>
       <c r="E65">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F65">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G65">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H65">
-        <v>0</v>
+        <v>14.29</v>
       </c>
     </row>
     <row r="66" spans="1:8">
@@ -2450,19 +2456,19 @@
         <v>72</v>
       </c>
       <c r="B66" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="C66" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D66">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E66">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F66">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G66">
         <v>0</v>
@@ -2476,19 +2482,19 @@
         <v>73</v>
       </c>
       <c r="B67" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C67" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D67">
         <v>12</v>
       </c>
       <c r="E67">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F67">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G67">
         <v>0</v>
@@ -2501,23 +2507,26 @@
       <c r="A68" t="s">
         <v>74</v>
       </c>
+      <c r="B68" t="s">
+        <v>117</v>
+      </c>
       <c r="C68" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D68">
+        <v>12</v>
+      </c>
+      <c r="E68">
         <v>5</v>
       </c>
-      <c r="E68">
-        <v>4</v>
-      </c>
       <c r="F68">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G68">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H68">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="69" spans="1:8">
@@ -2525,19 +2534,19 @@
         <v>75</v>
       </c>
       <c r="B69" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C69" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D69">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E69">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F69">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G69">
         <v>0</v>
@@ -2551,19 +2560,19 @@
         <v>76</v>
       </c>
       <c r="B70" t="s">
-        <v>115</v>
+        <v>94</v>
       </c>
       <c r="C70" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="D70">
         <v>5</v>
       </c>
       <c r="E70">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F70">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G70">
         <v>0</v>
@@ -2577,10 +2586,10 @@
         <v>77</v>
       </c>
       <c r="B71" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C71" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="D71">
         <v>4</v>
@@ -2589,7 +2598,7 @@
         <v>4</v>
       </c>
       <c r="F71">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G71">
         <v>0</v>
@@ -2603,7 +2612,7 @@
         <v>78</v>
       </c>
       <c r="B72" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D72">
         <v>6</v>
@@ -2612,30 +2621,27 @@
         <v>4</v>
       </c>
       <c r="F72">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G72">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H72">
-        <v>0</v>
+        <v>33.33</v>
       </c>
     </row>
     <row r="73" spans="1:8">
       <c r="A73" t="s">
         <v>79</v>
       </c>
-      <c r="B73" t="s">
-        <v>116</v>
-      </c>
       <c r="C73" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="D73">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E73">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F73">
         <v>0</v>
@@ -2652,16 +2658,16 @@
         <v>80</v>
       </c>
       <c r="B74" t="s">
-        <v>46</v>
+        <v>117</v>
       </c>
       <c r="C74" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="D74">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E74">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F74">
         <v>0</v>
@@ -2678,10 +2684,10 @@
         <v>81</v>
       </c>
       <c r="B75" t="s">
-        <v>46</v>
+        <v>117</v>
       </c>
       <c r="C75" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="D75">
         <v>3</v>
@@ -2690,7 +2696,7 @@
         <v>3</v>
       </c>
       <c r="F75">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G75">
         <v>0</v>
@@ -2704,25 +2710,25 @@
         <v>82</v>
       </c>
       <c r="B76" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C76" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="D76">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E76">
         <v>3</v>
       </c>
       <c r="F76">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G76">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H76">
-        <v>0</v>
+        <v>33.33</v>
       </c>
     </row>
     <row r="77" spans="1:8">
@@ -2730,19 +2736,19 @@
         <v>83</v>
       </c>
       <c r="B77" t="s">
-        <v>115</v>
+        <v>47</v>
       </c>
       <c r="C77" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="D77">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E77">
         <v>3</v>
       </c>
       <c r="F77">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G77">
         <v>0</v>
@@ -2756,10 +2762,10 @@
         <v>84</v>
       </c>
       <c r="B78" t="s">
-        <v>115</v>
+        <v>47</v>
       </c>
       <c r="C78" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="D78">
         <v>3</v>
@@ -2782,19 +2788,19 @@
         <v>85</v>
       </c>
       <c r="B79" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="C79" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="D79">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E79">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F79">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G79">
         <v>0</v>
@@ -2808,19 +2814,19 @@
         <v>86</v>
       </c>
       <c r="B80" t="s">
-        <v>117</v>
+        <v>47</v>
       </c>
       <c r="C80" t="s">
         <v>124</v>
       </c>
       <c r="D80">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E80">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F80">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G80">
         <v>0</v>
@@ -2834,16 +2840,16 @@
         <v>87</v>
       </c>
       <c r="B81" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C81" t="s">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="D81">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E81">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F81">
         <v>0</v>
@@ -2860,13 +2866,16 @@
         <v>88</v>
       </c>
       <c r="B82" t="s">
-        <v>46</v>
+        <v>118</v>
+      </c>
+      <c r="C82" t="s">
+        <v>126</v>
       </c>
       <c r="D82">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E82">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F82">
         <v>0</v>
@@ -2883,10 +2892,10 @@
         <v>89</v>
       </c>
       <c r="B83" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C83" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D83">
         <v>2</v>
@@ -2895,7 +2904,7 @@
         <v>2</v>
       </c>
       <c r="F83">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G83">
         <v>0</v>
@@ -2909,16 +2918,16 @@
         <v>90</v>
       </c>
       <c r="B84" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="C84" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="D84">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E84">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F84">
         <v>0</v>
@@ -2935,19 +2944,16 @@
         <v>91</v>
       </c>
       <c r="B85" t="s">
-        <v>46</v>
-      </c>
-      <c r="C85" t="s">
-        <v>122</v>
+        <v>47</v>
       </c>
       <c r="D85">
         <v>2</v>
       </c>
       <c r="E85">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F85">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G85">
         <v>0</v>
@@ -2961,19 +2967,19 @@
         <v>92</v>
       </c>
       <c r="B86" t="s">
-        <v>92</v>
+        <v>117</v>
       </c>
       <c r="C86" t="s">
-        <v>92</v>
+        <v>125</v>
       </c>
       <c r="D86">
-        <v>51</v>
+        <v>2</v>
       </c>
       <c r="E86">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F86">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G86">
         <v>0</v>
@@ -2987,16 +2993,16 @@
         <v>93</v>
       </c>
       <c r="B87" t="s">
-        <v>115</v>
+        <v>47</v>
       </c>
       <c r="C87" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="D87">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E87">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F87">
         <v>0</v>
@@ -3013,10 +3019,10 @@
         <v>94</v>
       </c>
       <c r="B88" t="s">
-        <v>46</v>
+        <v>120</v>
       </c>
       <c r="C88" t="s">
-        <v>119</v>
+        <v>130</v>
       </c>
       <c r="D88">
         <v>1</v>
@@ -3025,7 +3031,7 @@
         <v>1</v>
       </c>
       <c r="F88">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G88">
         <v>0</v>
@@ -3039,19 +3045,19 @@
         <v>95</v>
       </c>
       <c r="B89" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C89" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="D89">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E89">
         <v>1</v>
       </c>
       <c r="F89">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G89">
         <v>0</v>
@@ -3065,13 +3071,13 @@
         <v>96</v>
       </c>
       <c r="B90" t="s">
-        <v>116</v>
+        <v>96</v>
       </c>
       <c r="C90" t="s">
-        <v>124</v>
+        <v>96</v>
       </c>
       <c r="D90">
-        <v>1</v>
+        <v>51</v>
       </c>
       <c r="E90">
         <v>1</v>
@@ -3094,7 +3100,7 @@
         <v>117</v>
       </c>
       <c r="C91" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D91">
         <v>1</v>
@@ -3117,10 +3123,10 @@
         <v>98</v>
       </c>
       <c r="B92" t="s">
-        <v>117</v>
+        <v>47</v>
       </c>
       <c r="C92" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="D92">
         <v>1</v>
@@ -3143,10 +3149,10 @@
         <v>99</v>
       </c>
       <c r="B93" t="s">
-        <v>116</v>
+        <v>47</v>
       </c>
       <c r="C93" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="D93">
         <v>1</v>
@@ -3155,7 +3161,7 @@
         <v>1</v>
       </c>
       <c r="F93">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G93">
         <v>0</v>
@@ -3169,10 +3175,10 @@
         <v>100</v>
       </c>
       <c r="B94" t="s">
-        <v>46</v>
+        <v>118</v>
       </c>
       <c r="C94" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="D94">
         <v>1</v>
@@ -3195,10 +3201,10 @@
         <v>101</v>
       </c>
       <c r="B95" t="s">
-        <v>46</v>
+        <v>119</v>
       </c>
       <c r="C95" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="D95">
         <v>1</v>
@@ -3221,10 +3227,10 @@
         <v>102</v>
       </c>
       <c r="B96" t="s">
-        <v>46</v>
+        <v>119</v>
       </c>
       <c r="C96" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="D96">
         <v>1</v>
@@ -3247,10 +3253,10 @@
         <v>103</v>
       </c>
       <c r="B97" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="C97" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="D97">
         <v>1</v>
@@ -3262,10 +3268,10 @@
         <v>1</v>
       </c>
       <c r="G97">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H97">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98" spans="1:8">
@@ -3273,10 +3279,10 @@
         <v>104</v>
       </c>
       <c r="B98" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C98" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D98">
         <v>1</v>
@@ -3285,7 +3291,7 @@
         <v>1</v>
       </c>
       <c r="F98">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G98">
         <v>0</v>
@@ -3299,10 +3305,10 @@
         <v>105</v>
       </c>
       <c r="B99" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C99" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D99">
         <v>1</v>
@@ -3325,10 +3331,10 @@
         <v>106</v>
       </c>
       <c r="B100" t="s">
-        <v>46</v>
+        <v>117</v>
       </c>
       <c r="C100" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="D100">
         <v>1</v>
@@ -3351,10 +3357,10 @@
         <v>107</v>
       </c>
       <c r="B101" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C101" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="D101">
         <v>1</v>
@@ -3377,10 +3383,10 @@
         <v>108</v>
       </c>
       <c r="B102" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C102" t="s">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="D102">
         <v>1</v>
@@ -3389,7 +3395,7 @@
         <v>1</v>
       </c>
       <c r="F102">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G102">
         <v>0</v>
@@ -3403,10 +3409,10 @@
         <v>109</v>
       </c>
       <c r="B103" t="s">
-        <v>115</v>
+        <v>47</v>
       </c>
       <c r="C103" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="D103">
         <v>1</v>
@@ -3415,7 +3421,7 @@
         <v>1</v>
       </c>
       <c r="F103">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G103">
         <v>0</v>
@@ -3429,10 +3435,10 @@
         <v>110</v>
       </c>
       <c r="B104" t="s">
-        <v>117</v>
+        <v>47</v>
       </c>
       <c r="C104" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="D104">
         <v>1</v>
@@ -3441,13 +3447,13 @@
         <v>1</v>
       </c>
       <c r="F104">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G104">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H104">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="105" spans="1:8">
@@ -3455,10 +3461,10 @@
         <v>111</v>
       </c>
       <c r="B105" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C105" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="D105">
         <v>1</v>
@@ -3474,6 +3480,58 @@
       </c>
       <c r="H105">
         <v>0</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8">
+      <c r="A106" t="s">
+        <v>112</v>
+      </c>
+      <c r="B106" t="s">
+        <v>119</v>
+      </c>
+      <c r="C106" t="s">
+        <v>126</v>
+      </c>
+      <c r="D106">
+        <v>1</v>
+      </c>
+      <c r="E106">
+        <v>1</v>
+      </c>
+      <c r="F106">
+        <v>0</v>
+      </c>
+      <c r="G106">
+        <v>0</v>
+      </c>
+      <c r="H106">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8">
+      <c r="A107" t="s">
+        <v>113</v>
+      </c>
+      <c r="B107" t="s">
+        <v>47</v>
+      </c>
+      <c r="C107" t="s">
+        <v>121</v>
+      </c>
+      <c r="D107">
+        <v>1</v>
+      </c>
+      <c r="E107">
+        <v>0</v>
+      </c>
+      <c r="F107">
+        <v>1</v>
+      </c>
+      <c r="G107">
+        <v>1</v>
+      </c>
+      <c r="H107">
+        <v>100</v>
       </c>
     </row>
   </sheetData>

--- a/marketing_report/outputs/Grado_Pregrado/tabla_utm_campaigns.xlsx
+++ b/marketing_report/outputs/Grado_Pregrado/tabla_utm_campaigns.xlsx
@@ -807,7 +807,7 @@
         <v>13235</v>
       </c>
       <c r="E2">
-        <v>11766</v>
+        <v>11767</v>
       </c>
       <c r="F2">
         <v>5148</v>
@@ -830,19 +830,19 @@
         <v>121</v>
       </c>
       <c r="D3">
-        <v>8244</v>
+        <v>8237</v>
       </c>
       <c r="E3">
-        <v>6529</v>
+        <v>6530</v>
       </c>
       <c r="F3">
-        <v>6679</v>
+        <v>6680</v>
       </c>
       <c r="G3">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="H3">
-        <v>11.2</v>
+        <v>11.18</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -911,7 +911,7 @@
         <v>5324</v>
       </c>
       <c r="E6">
-        <v>4228</v>
+        <v>4227</v>
       </c>
       <c r="F6">
         <v>0</v>
@@ -943,10 +943,10 @@
         <v>4029</v>
       </c>
       <c r="G7">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H7">
-        <v>4.37</v>
+        <v>4.39</v>
       </c>
     </row>
     <row r="8" spans="1:8">
